--- a/data/describe/few_shot/cluster/messages_dog.xlsx
+++ b/data/describe/few_shot/cluster/messages_dog.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B25C6C8-068E-4FB7-AEBD-BE8270DC04EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{2A50AC59-E583-49FE-80B9-B26AD9FDF31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29805" yWindow="1920" windowWidth="20190" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34725" yWindow="3570" windowWidth="23370" windowHeight="16800"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>User</t>
   </si>
@@ -33,64 +33,87 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as lively and responsive?</t>
-  </si>
-  <si>
-    <t>A lively and responsive dog is incredibly playful, bursting with energy, and always eager for mental stimulation. They are also highly adaptable to new situations and quite keen on learning new things.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as calm and steady?</t>
-  </si>
-  <si>
-    <t>When a dog is described as calm and steady, it means they aren't overly playful or bursting with energy, and they don't demand constant mental stimulation. Such a dog is also not highly adaptable to new situations and might not be the quickest to pick up new tricks during training.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as relaxed and quiet?</t>
-  </si>
-  <si>
-    <t>When a dog is described as relaxed and quiet, picture a canine companion who typically enjoys a more mellow, lower energy lifestyle.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as social and adaptable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as social and adaptable, it means they are wonderfully affectionate with their family and show a natural ease with young children. These flexible companions also boast a good level of adaptability, and their drooling level is a minor characteristic often noted about them.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as amiable partner?</t>
-  </si>
-  <si>
-    <t>When a dog is described as an amiable partner, it means they generally have a friendly disposition and get along well with other dogs.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as vigilant guardian?</t>
-  </si>
-  <si>
-    <t>A dog described as a vigilant guardian will have a notable watchdog and protective nature, often accompanied by a moderate drooling level. These diligent companions also tend to require a fair amount of mental stimulation to keep them sharp and engaged.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as easygoing and free-spirited?</t>
-  </si>
-  <si>
-    <t>An easygoing and free-spirited dog is one that tends to get along well with other pups, showing a friendly and relaxed demeanor in social settings. You might also find that they are quite easy-maintenance when it comes to traits like shedding or drooling, adding to their carefree charm.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as aware and protective?</t>
-  </si>
-  <si>
-    <t>When a dog is described as aware and protective, it means they have a natural inclination to be a vigilant watchdog, ready to guard and protect their home and loved ones.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster:```Members of this cluster can be described as: relatively high on calm and steady, relatively high on social and adaptable, quite high on vigilant guardian, relatively low on easygoing and free-spirited```</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster:```Members of this cluster can be described as: relatively high on calm and steady, quite low on relaxed and quiet, slightly low on amiable partner, normal on easygoing and free-spirited```</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as: normal on lively and responsive, slightly high on social and adaptable, normal on vigilant guardian, quite high on aware and protective```</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and stable,  quite low on active and playful,  slightly low on self-reliant and composed,  normal on social and natural```</t>
+    <t>What does it mean when a dog is described as playful and energetic?</t>
+  </si>
+  <si>
+    <t>When a dog is described as playful and energetic, it means they are truly a bundle of joy, bursting with playfulness and high energy, always eager for fun and in need of exciting mental challenges to keep their clever mind engaged. These lively pups are also incredibly adaptable, ready to embrace new experiences, and respond well to training.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as calm and relaxed?</t>
+  </si>
+  <si>
+    <t>A calm and relaxed dog isn't particularly playful or energetic, nor do they crave lots of mental stimulation. Instead, they are less adaptable and may not be the easiest to train.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as active and vigorous?</t>
+  </si>
+  <si>
+    <t>When a dog is described as active and vigorous, it means they are quite energetic and full of life!</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adaptable and amiable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as adaptable and amiable, they are cherished companions, known for being affectionate with their family and wonderfully good with young children. These easygoing pups also show a good level of adaptability to new situations, and they might even exhibit a certain degree of drooling.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as social and gentle?</t>
+  </si>
+  <si>
+    <t>A social and gentle dog is one that tends to get along well with other dogs, showing a friendly and agreeable nature in canine company.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as protective and robust?</t>
+  </si>
+  <si>
+    <t>When a dog is described as protective and robust, it means they possess a strong watchdog and protective nature, often accompanied by a notable drooling level. These dogs also tend to have a considerable need for mental stimulation to keep their minds engaged.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as self-contained and tidy?</t>
+  </si>
+  <si>
+    <t>A self-contained and tidy dog isn't one to leave trails of drool or shed hair all over the house. These neat companions are also quite amiable, generally getting along well with other dogs.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as alert and watchful?</t>
+  </si>
+  <si>
+    <t>An alert and watchful dog is a true guardian, always ready to act as a watchdog with a strong protective nature.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are highly affectionate and adaptable with their human families, but tend to be less sociable with other dogs and are not particularly self-contained or tidy. Their primary strengths lie in their exceptional adaptability to new situations and their amiable nature, making them wonderfully affectionate with their family and good with young children. However, they exhibit significant weaknesses in their interactions with other dogs, often struggling to be social and gentle, and are also slightly less self-contained or tidy, indicating a tendency to drool or shed.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions. Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play. However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are dedicated protective guardians and affectionate family members, characterized by a calm disposition but a tendency to be less self-contained. Their key strengths include a strong watchdog and protective nature, deep affection for family and children due to their adaptable and amiable temperament, and a generally calm demeanor that doesn't demand constant high-energy play. However, their calm nature can mean they are less quick to learn new tricks or adapt to completely novel scenarios, and they are prone to drooling and shedding, as indicated by their lower self-contained and tidy score, which also implies they may not be as amicable with other dogs.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are primarily calm and relaxed, exhibiting very low energy levels, and showing a slight disinclination towards social interactions with other canines. Their primary strength lies in their profoundly calm and relaxed nature, making them ideal companions for individuals seeking a tranquil, low-energy pet that requires minimal physical or mental stimulation. However, they are notably unsuited for highly active households, may be less adaptable or quick to learn new things, and tend to be less social and gentle in their interactions with other dogs.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are notably alert and watchful guardians, combining a good level of adaptability and affection with average energy and protective traits. Their primary strengths lie in their exceptional vigilance as watchdogs and protectors, complemented by their affectionate nature towards family and children, and their good adaptability to new situations. While generally well-rounded, their energy levels are only at a normal level, meaning they are not particularly bursting with playfulness or requiring constant high-energy activities.</t>
+  </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+I will provided you with the cluster description and you will return the summary.
+Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  normal on playful and energetic,  relatively high on adaptable and amiable,  quite low on social and gentle,  slightly low on self-contained and tidy´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  quite low on playful and energetic,  slightly low on active and vigorous,  slightly high on protective and robust,  slightly low on self-contained and tidy´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and relaxed,  relatively high on adaptable and amiable,  quite high on protective and robust,  relatively low on self-contained and tidy´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and relaxed,  quite low on active and vigorous,  slightly low on social and gentle,  normal on self-contained and tidy´´´</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -101,55 +124,14 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  normal on lively and responsive,  relatively high on social and adaptable,  quite low on amiable partner,  slightly low on easygoing and free-spirited```</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary.
-Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as: quite low on lively and responsive, slightly low on relaxed and quiet, slightly high on vigilant guardian, slightly low on easygoing and free-spirited``` </t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are generally low in playfulness and high energy, tend not to be consistently relaxed, but possess some protective instincts and are not particularly easygoing with other dogs.
-Their primary strength lies in their slightly elevated vigilant guardian trait, which means they can offer a degree of watchdog and protective capabilities for their home and family.
-However, they are less inclined to be adaptable or quick to learn, may not get along well with other dogs, are not consistently mellow, and can be less easy-maintenance.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are dedicated protective guardians and affectionate family members, characterized by a calm disposition but a less easygoing nature with other dogs.
-They excel as vigilant guardians with a strong protective instinct, offering a calm presence that doesn't demand excessive physical energy, and are wonderfully affectionate with their family and children, demonstrating good adaptability within their home environment.
-However, their calm and steady nature suggests they may be less quick to learn new tricks or adapt to entirely new and challenging situations, and they are less easygoing in their interactions with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are predominantly calm and steady in nature, yet they are not typically relaxed or quiet, and show a slight disinclination towards amiability with other dogs, while maintaining an average level of general easygoing and free-spirited traits.
-Their primary strength lies in their composed and unwavering demeanor, meaning they do not demand constant mental stimulation or high-energy activities.
-However, their 'calm and steady' nature suggests they might not be highly adaptable or quick to learn new tricks, and their lower amiability means they may not get along well with other dogs, while also not exhibiting a truly relaxed or quiet, low-energy lifestyle.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are highly aware and protective, with a slightly above-average social and adaptable nature, and normal levels of liveliness, responsiveness, and guardianship.
-Their primary strength lies in their strong inclination to be vigilant watchdogs, ready to guard and protect, complemented by their affectionate nature with family and ease with children due to their adaptability.
-While their protective nature is a valuable asset, it may also require dedicated training and socialization to ensure these strong guarding instincts are appropriately channeled and don't lead to undue wariness, and their normal energy levels mean they are not particularly demanding in terms of constant activity.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are generally calm and stable, with low levels of activity and playfulness, and are slightly less self-reliant, while being average in their social tendencies.
-Their primary strength lies in their calm and stable demeanor, meaning they don't demand extensive mental stimulation or high-energy activities.
-However, they are less inclined towards active play and might be less adaptable to new situations, and they may also exhibit less composure or independence when interacting with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are notably social and adaptable with people, while exhibiting average levels of liveliness and responsiveness, but tend to be less amiable and easygoing, particularly with other dogs.
-Their primary strengths are their strong affection for family, ease with young children, and a good level of adaptability to new situations, all while maintaining a normal capacity for play and mental stimulation.
-However, a key weakness is their tendency to not get along well with other canines, often struggling to be friendly, relaxed, or easygoing in social settings with other dogs.</t>
+Now do the same thing with the following: ```Members of this cluster can be described as:  normal on playful and energetic,  slightly high on adaptable and amiable,  normal on protective and robust,  quite high on alert and watchful´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,20 +140,321 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -180,38 +463,212 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -234,44 +691,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -298,14 +755,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -332,6 +807,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -343,176 +836,152 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="69.453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="96.26953125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="76.54296875" customWidth="1"/>
+    <col min="2" max="2" width="92.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -523,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -531,7 +1000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -539,7 +1008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -547,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -555,7 +1024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -563,7 +1032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -571,7 +1040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -579,7 +1048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -587,55 +1056,48 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="232" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="130" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="120" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/describe/few_shot/cluster/messages_dog.xlsx
+++ b/data/describe/few_shot/cluster/messages_dog.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{2A50AC59-E583-49FE-80B9-B26AD9FDF31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55530006-00DF-4C06-90FC-38592AD5D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34725" yWindow="3570" windowWidth="23370" windowHeight="16800"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>User</t>
   </si>
@@ -33,67 +33,49 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as playful and energetic?</t>
-  </si>
-  <si>
-    <t>When a dog is described as playful and energetic, it means they are truly a bundle of joy, bursting with playfulness and high energy, always eager for fun and in need of exciting mental challenges to keep their clever mind engaged. These lively pups are also incredibly adaptable, ready to embrace new experiences, and respond well to training.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as calm and relaxed?</t>
-  </si>
-  <si>
-    <t>A calm and relaxed dog isn't particularly playful or energetic, nor do they crave lots of mental stimulation. Instead, they are less adaptable and may not be the easiest to train.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as active and vigorous?</t>
-  </si>
-  <si>
-    <t>When a dog is described as active and vigorous, it means they are quite energetic and full of life!</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as adaptable and amiable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as adaptable and amiable, they are cherished companions, known for being affectionate with their family and wonderfully good with young children. These easygoing pups also show a good level of adaptability to new situations, and they might even exhibit a certain degree of drooling.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as social and gentle?</t>
-  </si>
-  <si>
-    <t>A social and gentle dog is one that tends to get along well with other dogs, showing a friendly and agreeable nature in canine company.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as protective and robust?</t>
-  </si>
-  <si>
-    <t>When a dog is described as protective and robust, it means they possess a strong watchdog and protective nature, often accompanied by a notable drooling level. These dogs also tend to have a considerable need for mental stimulation to keep their minds engaged.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as self-contained and tidy?</t>
-  </si>
-  <si>
-    <t>A self-contained and tidy dog isn't one to leave trails of drool or shed hair all over the house. These neat companions are also quite amiable, generally getting along well with other dogs.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as alert and watchful?</t>
-  </si>
-  <si>
-    <t>An alert and watchful dog is a true guardian, always ready to act as a watchdog with a strong protective nature.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are highly affectionate and adaptable with their human families, but tend to be less sociable with other dogs and are not particularly self-contained or tidy. Their primary strengths lie in their exceptional adaptability to new situations and their amiable nature, making them wonderfully affectionate with their family and good with young children. However, they exhibit significant weaknesses in their interactions with other dogs, often struggling to be social and gentle, and are also slightly less self-contained or tidy, indicating a tendency to drool or shed.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions. Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play. However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are dedicated protective guardians and affectionate family members, characterized by a calm disposition but a tendency to be less self-contained. Their key strengths include a strong watchdog and protective nature, deep affection for family and children due to their adaptable and amiable temperament, and a generally calm demeanor that doesn't demand constant high-energy play. However, their calm nature can mean they are less quick to learn new tricks or adapt to completely novel scenarios, and they are prone to drooling and shedding, as indicated by their lower self-contained and tidy score, which also implies they may not be as amicable with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are primarily calm and relaxed, exhibiting very low energy levels, and showing a slight disinclination towards social interactions with other canines. Their primary strength lies in their profoundly calm and relaxed nature, making them ideal companions for individuals seeking a tranquil, low-energy pet that requires minimal physical or mental stimulation. However, they are notably unsuited for highly active households, may be less adaptable or quick to learn new things, and tend to be less social and gentle in their interactions with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are notably alert and watchful guardians, combining a good level of adaptability and affection with average energy and protective traits. Their primary strengths lie in their exceptional vigilance as watchdogs and protectors, complemented by their affectionate nature towards family and children, and their good adaptability to new situations. While generally well-rounded, their energy levels are only at a normal level, meaning they are not particularly bursting with playfulness or requiring constant high-energy activities.</t>
+    <t>What does it mean when a dog is described as active?</t>
+  </si>
+  <si>
+    <t>When a dog is described as active, it means that they have a high level of playfulness, energy, and need for mental stimulation, making them lively companions who thrive on interaction and exercise. Additionally, their strong adaptability and trainability suggest they are eager to engage with their environment and learn new things, making them dynamic members of any household.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as not active?</t>
+  </si>
+  <si>
+    <t>When a dog is described as not active, it means they are not playful, lack energy, and have minimal need for mental stimulation. This type of dog tends to prefer a more relaxed lifestyle, showing little enthusiasm for physical activities and having low adaptability to new environments.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as energetic?</t>
+  </si>
+  <si>
+    <t>When a dog is described as energetic, it means they have a lively spirit and a noticeable energy level that makes them eager to play and explore. This enthusiasm for activity can bring a sense of joy and vitality to any environment, making them the perfect companions for those who love an active lifestyle!</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adaptable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as adaptable, it means that the dog can adjust to various situations and environments with relative ease, although not in an outstanding or highly noticeable way. This versatility includes being affectionate with family, getting along well with young children, and showing some flexibility when it comes to different experiences, all while possibly having a bit of drooling on the side.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as sociable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as sociable, it means they have a friendly demeanor and get along well with other dogs, even if this trait is only slightly pronounced. This sociable nature makes them more inclined to engage positively with their furry friends, showcasing a willingness to socialize and play.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as watchful?</t>
+  </si>
+  <si>
+    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on whatâ€™s happening around them.</t>
+  </si>
+  <si>
+    <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as reserved?</t>
+  </si>
+  <si>
+    <t>When a dog is described as reserved, it indicates that they tend to be more independent and cautious, showing a protective nature that makes them alert as a watchdog. This means they might not seek out the company of other dogs as eagerly and are likely to be more selective about their interactions.</t>
   </si>
   <si>
     <t>Thats really good. You truly understand the factors and names. 
@@ -104,16 +86,10 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 I will provided you with the cluster description and you will return the summary.
-Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  normal on playful and energetic,  relatively high on adaptable and amiable,  quite low on social and gentle,  slightly low on self-contained and tidy´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  quite low on playful and energetic,  slightly low on active and vigorous,  slightly high on protective and robust,  slightly low on self-contained and tidy´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and relaxed,  relatively high on adaptable and amiable,  quite high on protective and robust,  relatively low on self-contained and tidy´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and relaxed,  quite low on active and vigorous,  slightly low on social and gentle,  normal on self-contained and tidy´´´</t>
+Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  slightly high on not active,  quite high on adaptable,  relatively high on watchful,  relatively low on sociable´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively low on active,  relatively low on energetic,  normal on sociable,  relatively low on sociable´´´</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -124,14 +100,23 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  normal on playful and energetic,  slightly high on adaptable and amiable,  normal on protective and robust,  quite high on alert and watchful´´´</t>
+Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on not active,  normal on adaptable,  slightly low on sociable,  relatively high on reserved´´´</t>
+  </si>
+  <si>
+    <t>This cluster comprises dogs that exhibit a more laid-back demeanor, being slightly high on not being active while also displaying adaptability and watchfulness. A strength of this group lies in their adaptability, making them suitable for a variety of living situations and environments while maintaining a watchful eye on their surroundings. However, they may struggle in social settings, as their relatively low sociability could hinder interactions with other dogs and people.</t>
+  </si>
+  <si>
+    <t>This cluster consists of dogs that exhibit lower levels of activity and energy, presenting a more laid-back demeanor. They tend to be reasonably sociable, indicating that while they may not be the most outgoing, they are generally friendly in social situations. However, their relatively low scores on both active and energetic suggest they may not thrive in high-energy environments or require less physical engagement, which could limit their appeal to more active households.</t>
+  </si>
+  <si>
+    <t>This cluster represents dogs that are generally less active, displaying a balanced adaptability, while tending to be more reserved. Their specific strength lies in their adaptability, which allows them to adjust well to various environments and situations. However, their slight lack of sociability may limit their interactions with people and other dogs, potentially hindering social development and companionship.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +247,20 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -614,13 +613,22 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -976,12 +984,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="76.54296875" customWidth="1"/>
-    <col min="2" max="2" width="92.08984375" customWidth="1"/>
+    <col min="1" max="1" width="64.08984375" customWidth="1"/>
+    <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -992,7 +1000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1000,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="36" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +1016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1016,7 +1024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1024,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1032,7 +1040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1040,59 +1048,43 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="136.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="130" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="51.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="120" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/describe/few_shot/cluster/messages_dog.xlsx
+++ b/data/describe/few_shot/cluster/messages_dog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55530006-00DF-4C06-90FC-38592AD5D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A42545-D601-4CAF-8726-28812CBE8502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>What does it mean when a dog is described as watchful?</t>
   </si>
   <si>
-    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on whatâ€™s happening around them.</t>
-  </si>
-  <si>
     <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
   </si>
   <si>
@@ -103,13 +100,16 @@
 Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on not active,  normal on adaptable,  slightly low on sociable,  relatively high on reserved´´´</t>
   </si>
   <si>
-    <t>This cluster comprises dogs that exhibit a more laid-back demeanor, being slightly high on not being active while also displaying adaptability and watchfulness. A strength of this group lies in their adaptability, making them suitable for a variety of living situations and environments while maintaining a watchful eye on their surroundings. However, they may struggle in social settings, as their relatively low sociability could hinder interactions with other dogs and people.</t>
-  </si>
-  <si>
-    <t>This cluster consists of dogs that exhibit lower levels of activity and energy, presenting a more laid-back demeanor. They tend to be reasonably sociable, indicating that while they may not be the most outgoing, they are generally friendly in social situations. However, their relatively low scores on both active and energetic suggest they may not thrive in high-energy environments or require less physical engagement, which could limit their appeal to more active households.</t>
-  </si>
-  <si>
-    <t>This cluster represents dogs that are generally less active, displaying a balanced adaptability, while tending to be more reserved. Their specific strength lies in their adaptability, which allows them to adjust well to various environments and situations. However, their slight lack of sociability may limit their interactions with people and other dogs, potentially hindering social development and companionship.</t>
+    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on what's happening around them.</t>
+  </si>
+  <si>
+    <t>These dogs thrives on observation rather than action. They are the ultimate chameleons: highly adaptable and unfazed by changing environments. While their watchfulness makes them excellent companions, their low social drive is a notable trade-off. These aren't 'greet-everyone-with-a-wag' dogs; they are selective and reserved, requiring a patient hand when navigating new faces and four-legged friends.</t>
+  </si>
+  <si>
+    <t>They are the introverted extroverts of the dog world, social enough to be friendly, but far too relaxed to be restless. Their strength is their steady, unshakeable vibe, making them low-maintenance. Just keep in mind that they are 'low-battery' by nature; they’ll choose a cozy rug over a long run every time, making them a specialized fit for low-energy environments.</t>
+  </si>
+  <si>
+    <t>These dogs with a soulful, reserved nature who prefer the quiet side of life. Their greatest asset is their effortless adaptability: they are the ultimate 'chameleons,' capable of settling into almost any living situation with ease. While they may never be the life of the dog park, their preference for a smaller inner circle makes them deeply loyal, one-on-one companions for those who appreciate a more tranquil bond.</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1045,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
@@ -1053,28 +1053,28 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="136.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="51.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>21</v>
@@ -1082,9 +1082,9 @@
     </row>
     <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/describe/few_shot/cluster/messages_dog.xlsx
+++ b/data/describe/few_shot/cluster/messages_dog.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A42545-D601-4CAF-8726-28812CBE8502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{44D2963D-7AE7-49C3-9699-67694EE14E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>User</t>
   </si>
@@ -33,90 +33,71 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as active?</t>
-  </si>
-  <si>
-    <t>When a dog is described as active, it means that they have a high level of playfulness, energy, and need for mental stimulation, making them lively companions who thrive on interaction and exercise. Additionally, their strong adaptability and trainability suggest they are eager to engage with their environment and learn new things, making them dynamic members of any household.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as not active?</t>
-  </si>
-  <si>
-    <t>When a dog is described as not active, it means they are not playful, lack energy, and have minimal need for mental stimulation. This type of dog tends to prefer a more relaxed lifestyle, showing little enthusiasm for physical activities and having low adaptability to new environments.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as energetic?</t>
-  </si>
-  <si>
-    <t>When a dog is described as energetic, it means they have a lively spirit and a noticeable energy level that makes them eager to play and explore. This enthusiasm for activity can bring a sense of joy and vitality to any environment, making them the perfect companions for those who love an active lifestyle!</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as adaptable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as adaptable, it means that the dog can adjust to various situations and environments with relative ease, although not in an outstanding or highly noticeable way. This versatility includes being affectionate with family, getting along well with young children, and showing some flexibility when it comes to different experiences, all while possibly having a bit of drooling on the side.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as sociable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as sociable, it means they have a friendly demeanor and get along well with other dogs, even if this trait is only slightly pronounced. This sociable nature makes them more inclined to engage positively with their furry friends, showcasing a willingness to socialize and play.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as watchful?</t>
-  </si>
-  <si>
-    <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as reserved?</t>
-  </si>
-  <si>
-    <t>When a dog is described as reserved, it indicates that they tend to be more independent and cautious, showing a protective nature that makes them alert as a watchdog. This means they might not seek out the company of other dogs as eagerly and are likely to be more selective about their interactions.</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary.
-Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  slightly high on not active,  quite high on adaptable,  relatively high on watchful,  relatively low on sociable´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively low on active,  relatively low on energetic,  normal on sociable,  relatively low on sociable´´´</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on not active,  normal on adaptable,  slightly low on sociable,  relatively high on reserved´´´</t>
-  </si>
-  <si>
-    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on what's happening around them.</t>
-  </si>
-  <si>
-    <t>These dogs thrives on observation rather than action. They are the ultimate chameleons: highly adaptable and unfazed by changing environments. While their watchfulness makes them excellent companions, their low social drive is a notable trade-off. These aren't 'greet-everyone-with-a-wag' dogs; they are selective and reserved, requiring a patient hand when navigating new faces and four-legged friends.</t>
-  </si>
-  <si>
-    <t>They are the introverted extroverts of the dog world, social enough to be friendly, but far too relaxed to be restless. Their strength is their steady, unshakeable vibe, making them low-maintenance. Just keep in mind that they are 'low-battery' by nature; they’ll choose a cozy rug over a long run every time, making them a specialized fit for low-energy environments.</t>
-  </si>
-  <si>
-    <t>These dogs with a soulful, reserved nature who prefer the quiet side of life. Their greatest asset is their effortless adaptability: they are the ultimate 'chameleons,' capable of settling into almost any living situation with ease. While they may never be the life of the dog park, their preference for a smaller inner circle makes them deeply loyal, one-on-one companions for those who appreciate a more tranquil bond.</t>
+    <t>What does it mean when a dog is described as short and sleek?</t>
+  </si>
+  <si>
+    <t>When a dog is described as short and sleek, picture a pup whose coat is wonderfully short and incredibly smooth to the touch.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as medium and layered?</t>
+  </si>
+  <si>
+    <t>A dog described as medium and layered boasts a beautiful medium-length double coat. Keeping this stunning coat in top condition means that its grooming frequency is a consideration.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as neat and simple?</t>
+  </si>
+  <si>
+    <t>A neat and simple dog is one that sports a coat that is either short or medium in length.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as flowing and maintained?</t>
+  </si>
+  <si>
+    <t>A dog with a flowing and maintained look boasts a long coat that absolutely demands regular grooming to keep it pristine. This magnificent mane often has a beautiful, silky texture.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as calm and placid?</t>
+  </si>
+  <si>
+    <t>When a dog is described as calm and placid, it means that the dog is not spirited and responsive. Instead of seeking mental stimulation, playfulness, or high energy, a calm and placid dog embodies a serene and relaxed demeanor, embracing a peaceful existence without the urge for excitement or activity.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as spirited and responsive?</t>
+  </si>
+  <si>
+    <t>When a dog is described as spirited and responsive, it means they are full of energy and enthusiasm, always eager for play and mental challenges. With high levels of playfulness, energy, and a keen need for mental stimulation, they are not just lively companions but also quick to learn and adapt, making them delightful and engaging pets.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as genial and adjustable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as genial and adjustable, it means this furry friend is welcoming and friendly, showing an openness to strangers that makes them a joy to be around. They are also adaptable, able to adjust to various situations, such as being good with young children and other dogs, which adds a playful energy to their personality.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as inquisitive and bright?</t>
+  </si>
+  <si>
+    <t>When a dog is described as inquisitive and bright, it means that this furry friend has a curious nature and an eagerness to explore the world around them. Their need for mental stimulation reflects their intelligent and alert personality, hinting at a playful mind that thrives on discovering new things!</t>
+  </si>
+  <si>
+    <t>From your answers I see that you have all the information you need about the factors. We are now going to do the most important task: provide a description of a cluster. Make sure you continue to use the same format and style as in earlier examples. This is the last description task to complete, so please pay close attention. You will receive information about the cluster based on the latent factors that best describe it. For each cluster, write a concise summary based on the available information. The first sentence should give an overview of the cluster. The second sentence should describe the cluster’s specific strengths based on the available information, if any exists. The third sentence should describe the cluster’s specific weaknesses based on the available information, if any exists. Now do this task based on the following description: ```Members of this cluster can be described as: quite high on medium and layered, slightly low on neat and simple, relatively low on calm and placid, slightly low on genial and adjustable´´´</t>
+  </si>
+  <si>
+    <t>These dogs possess a medium and layered appearance, indicating a balanced and versatile physical trait. Strengths of this cluster include their adaptability, which may allow them to thrive in various environments and roles. However, they may struggle with being overly neat and simple, as well as a tendency towards less calmness and placidity, potentially leading to a more energetic or chaotic demeanor.</t>
+  </si>
+  <si>
+    <t>These dogs are characterized by their spirited and responsive nature, as well as their inquisitive and bright demeanor. Their strengths lie in their high levels of energy and curiosity, making them engaging companions that are eager to explore their surroundings and interact with people. However, they may struggle with being less neat and simple in their appearance, as well as having a lower tendency to exhibit a short and sleek coat, which could be perceived as a lack of polish in their overall presentation.</t>
+  </si>
+  <si>
+    <t>Now do this task based on the following description: ```Members of this cluster can be described as: quite low on short and sleek, slightly low on neat and simple, relatively high on spirited and responsive, slightly high on inquisitive and bright´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,26 +231,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -613,22 +574,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -984,112 +933,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.08984375" customWidth="1"/>
-    <col min="2" max="2" width="67" customWidth="1"/>
+    <col min="1" max="1" width="63.7265625" customWidth="1"/>
+    <col min="2" max="2" width="53.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="36" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="136.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>